--- a/Sayajirao_Hall_Seat_Template.xlsx
+++ b/Sayajirao_Hall_Seat_Template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,21 +28,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -51,6 +36,16 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00888888"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -58,6 +53,11 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00222222"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -72,11 +72,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CCCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00222222"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,27 +93,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -489,69 +481,69 @@
   <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="4.5" customWidth="1" min="2" max="2"/>
-    <col width="4.5" customWidth="1" min="3" max="3"/>
-    <col width="4.5" customWidth="1" min="4" max="4"/>
-    <col width="4.5" customWidth="1" min="5" max="5"/>
-    <col width="4.5" customWidth="1" min="6" max="6"/>
-    <col width="4.5" customWidth="1" min="7" max="7"/>
-    <col width="4.5" customWidth="1" min="8" max="8"/>
-    <col width="4.5" customWidth="1" min="9" max="9"/>
-    <col width="4.5" customWidth="1" min="10" max="10"/>
-    <col width="4.5" customWidth="1" min="11" max="11"/>
-    <col width="4.5" customWidth="1" min="12" max="12"/>
-    <col width="4.5" customWidth="1" min="13" max="13"/>
-    <col width="4.5" customWidth="1" min="14" max="14"/>
-    <col width="4.5" customWidth="1" min="15" max="15"/>
-    <col width="4.5" customWidth="1" min="16" max="16"/>
-    <col width="4.5" customWidth="1" min="17" max="17"/>
-    <col width="4.5" customWidth="1" min="18" max="18"/>
-    <col width="4.5" customWidth="1" min="19" max="19"/>
-    <col width="4.5" customWidth="1" min="20" max="20"/>
-    <col width="4.5" customWidth="1" min="21" max="21"/>
-    <col width="4.5" customWidth="1" min="22" max="22"/>
-    <col width="4.5" customWidth="1" min="23" max="23"/>
-    <col width="4.5" customWidth="1" min="24" max="24"/>
-    <col width="4.5" customWidth="1" min="25" max="25"/>
-    <col width="4.5" customWidth="1" min="26" max="26"/>
-    <col width="4.5" customWidth="1" min="27" max="27"/>
-    <col width="4.5" customWidth="1" min="28" max="28"/>
-    <col width="4.5" customWidth="1" min="29" max="29"/>
-    <col width="4.5" customWidth="1" min="30" max="30"/>
-    <col width="4.5" customWidth="1" min="31" max="31"/>
-    <col width="4.5" customWidth="1" min="32" max="32"/>
-    <col width="4.5" customWidth="1" min="33" max="33"/>
-    <col width="4.5" customWidth="1" min="34" max="34"/>
-    <col width="4.5" customWidth="1" min="35" max="35"/>
-    <col width="4.5" customWidth="1" min="36" max="36"/>
-    <col width="4.5" customWidth="1" min="37" max="37"/>
-    <col width="4.5" customWidth="1" min="38" max="38"/>
-    <col width="4.5" customWidth="1" min="39" max="39"/>
-    <col width="4.5" customWidth="1" min="40" max="40"/>
-    <col width="4.5" customWidth="1" min="41" max="41"/>
-    <col width="4.5" customWidth="1" min="42" max="42"/>
-    <col width="4.5" customWidth="1" min="43" max="43"/>
-    <col width="4.5" customWidth="1" min="44" max="44"/>
-    <col width="4.5" customWidth="1" min="45" max="45"/>
-    <col width="4.5" customWidth="1" min="46" max="46"/>
-    <col width="4.5" customWidth="1" min="47" max="47"/>
-    <col width="4.5" customWidth="1" min="48" max="48"/>
-    <col width="4.5" customWidth="1" min="49" max="49"/>
-    <col width="4.5" customWidth="1" min="50" max="50"/>
-    <col width="4.5" customWidth="1" min="51" max="51"/>
-    <col width="4.5" customWidth="1" min="52" max="52"/>
-    <col width="4.5" customWidth="1" min="53" max="53"/>
-    <col width="4.5" customWidth="1" min="54" max="54"/>
-    <col width="4.5" customWidth="1" min="55" max="55"/>
-    <col width="4.5" customWidth="1" min="56" max="56"/>
-    <col width="4.5" customWidth="1" min="57" max="57"/>
-    <col width="4.5" customWidth="1" min="58" max="58"/>
-    <col width="4.5" customWidth="1" min="59" max="59"/>
-    <col width="4.5" customWidth="1" min="60" max="60"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6.5" customWidth="1" min="2" max="2"/>
+    <col width="6.5" customWidth="1" min="3" max="3"/>
+    <col width="6.5" customWidth="1" min="4" max="4"/>
+    <col width="6.5" customWidth="1" min="5" max="5"/>
+    <col width="6.5" customWidth="1" min="6" max="6"/>
+    <col width="6.5" customWidth="1" min="7" max="7"/>
+    <col width="6.5" customWidth="1" min="8" max="8"/>
+    <col width="6.5" customWidth="1" min="9" max="9"/>
+    <col width="6.5" customWidth="1" min="10" max="10"/>
+    <col width="6.5" customWidth="1" min="11" max="11"/>
+    <col width="6.5" customWidth="1" min="12" max="12"/>
+    <col width="6.5" customWidth="1" min="13" max="13"/>
+    <col width="6.5" customWidth="1" min="14" max="14"/>
+    <col width="6.5" customWidth="1" min="15" max="15"/>
+    <col width="6.5" customWidth="1" min="16" max="16"/>
+    <col width="6.5" customWidth="1" min="17" max="17"/>
+    <col width="6.5" customWidth="1" min="18" max="18"/>
+    <col width="6.5" customWidth="1" min="19" max="19"/>
+    <col width="6.5" customWidth="1" min="20" max="20"/>
+    <col width="6.5" customWidth="1" min="21" max="21"/>
+    <col width="6.5" customWidth="1" min="22" max="22"/>
+    <col width="6.5" customWidth="1" min="23" max="23"/>
+    <col width="6.5" customWidth="1" min="24" max="24"/>
+    <col width="6.5" customWidth="1" min="25" max="25"/>
+    <col width="6.5" customWidth="1" min="26" max="26"/>
+    <col width="6.5" customWidth="1" min="27" max="27"/>
+    <col width="6.5" customWidth="1" min="28" max="28"/>
+    <col width="6.5" customWidth="1" min="29" max="29"/>
+    <col width="6.5" customWidth="1" min="30" max="30"/>
+    <col width="6.5" customWidth="1" min="31" max="31"/>
+    <col width="6.5" customWidth="1" min="32" max="32"/>
+    <col width="6.5" customWidth="1" min="33" max="33"/>
+    <col width="6.5" customWidth="1" min="34" max="34"/>
+    <col width="6.5" customWidth="1" min="35" max="35"/>
+    <col width="6.5" customWidth="1" min="36" max="36"/>
+    <col width="6.5" customWidth="1" min="37" max="37"/>
+    <col width="6.5" customWidth="1" min="38" max="38"/>
+    <col width="6.5" customWidth="1" min="39" max="39"/>
+    <col width="6.5" customWidth="1" min="40" max="40"/>
+    <col width="6.5" customWidth="1" min="41" max="41"/>
+    <col width="6.5" customWidth="1" min="42" max="42"/>
+    <col width="6.5" customWidth="1" min="43" max="43"/>
+    <col width="6.5" customWidth="1" min="44" max="44"/>
+    <col width="6.5" customWidth="1" min="45" max="45"/>
+    <col width="6.5" customWidth="1" min="46" max="46"/>
+    <col width="6.5" customWidth="1" min="47" max="47"/>
+    <col width="6.5" customWidth="1" min="48" max="48"/>
+    <col width="6.5" customWidth="1" min="49" max="49"/>
+    <col width="6.5" customWidth="1" min="50" max="50"/>
+    <col width="6.5" customWidth="1" min="51" max="51"/>
+    <col width="6.5" customWidth="1" min="52" max="52"/>
+    <col width="6.5" customWidth="1" min="53" max="53"/>
+    <col width="6.5" customWidth="1" min="54" max="54"/>
+    <col width="6.5" customWidth="1" min="55" max="55"/>
+    <col width="6.5" customWidth="1" min="56" max="56"/>
+    <col width="6.5" customWidth="1" min="57" max="57"/>
+    <col width="6.5" customWidth="1" min="58" max="58"/>
+    <col width="6.5" customWidth="1" min="59" max="59"/>
+    <col width="4" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sayjirao Nagar Gruha, Akota, Vadodara</t>
@@ -559,4284 +551,4284 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>S T A G E</t>
         </is>
       </c>
     </row>
     <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="3" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="Q4" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="S4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W4" s="5" t="n"/>
-      <c r="X4" s="5" t="n"/>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="n"/>
-      <c r="AA4" s="5" t="n"/>
-      <c r="AB4" s="4" t="n">
+      <c r="Z4" s="6" t="n"/>
+      <c r="AA4" s="6" t="n"/>
+      <c r="AB4" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AD4" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AE4" s="4" t="n">
+      <c r="AE4" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AF4" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AG4" s="4" t="n">
+      <c r="AG4" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AH4" s="4" t="n">
+      <c r="AH4" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AI4" s="4" t="n">
+      <c r="AI4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ4" s="4" t="n">
+      <c r="AJ4" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AK4" s="4" t="n">
+      <c r="AK4" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL4" s="4" t="n">
+      <c r="AL4" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AM4" s="5" t="n"/>
-      <c r="AN4" s="5" t="n"/>
-      <c r="AO4" s="5" t="n"/>
-      <c r="AP4" s="5" t="n"/>
-      <c r="AQ4" s="5" t="n"/>
-      <c r="AR4" s="3" t="inlineStr">
+      <c r="AM4" s="6" t="n"/>
+      <c r="AN4" s="6" t="n"/>
+      <c r="AO4" s="6" t="n"/>
+      <c r="AP4" s="6" t="n"/>
+      <c r="AQ4" s="6" t="n"/>
+      <c r="AR4" s="4" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="AS4" s="4" t="n">
+      <c r="AS4" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AT4" s="4" t="n">
+      <c r="AT4" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AU4" s="4" t="n">
+      <c r="AU4" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AV4" s="4" t="n">
+      <c r="AV4" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AW4" s="4" t="n">
+      <c r="AW4" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AX4" s="4" t="n">
+      <c r="AX4" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AY4" s="4" t="n">
+      <c r="AY4" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AZ4" s="4" t="n">
+      <c r="AZ4" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="BA4" s="4" t="n">
+      <c r="BA4" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="BB4" s="4" t="n">
+      <c r="BB4" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="BC4" s="4" t="n">
+      <c r="BC4" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BD4" s="4" t="n">
+      <c r="BD4" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BE4" s="3" t="inlineStr">
+      <c r="BE4" s="4" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="n"/>
-      <c r="BG4" s="2" t="n"/>
-      <c r="BH4" s="2" t="n"/>
+      <c r="BF4" s="3" t="n"/>
+      <c r="BG4" s="3" t="n"/>
+      <c r="BH4" s="3" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="3" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="Q5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="R5" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="S5" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="T5" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="V5" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="Z5" s="5" t="n"/>
-      <c r="AA5" s="5" t="n"/>
-      <c r="AB5" s="4" t="n">
+      <c r="Z5" s="6" t="n"/>
+      <c r="AA5" s="6" t="n"/>
+      <c r="AB5" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AD5" s="4" t="n">
+      <c r="AD5" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AE5" s="4" t="n">
+      <c r="AE5" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AF5" s="4" t="n">
+      <c r="AF5" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AG5" s="4" t="n">
+      <c r="AG5" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AH5" s="4" t="n">
+      <c r="AH5" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AI5" s="4" t="n">
+      <c r="AI5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ5" s="4" t="n">
+      <c r="AJ5" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AK5" s="4" t="n">
+      <c r="AK5" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL5" s="4" t="n">
+      <c r="AL5" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AM5" s="5" t="n"/>
-      <c r="AN5" s="5" t="n"/>
-      <c r="AO5" s="5" t="n"/>
-      <c r="AP5" s="5" t="n"/>
-      <c r="AQ5" s="5" t="n"/>
-      <c r="AR5" s="3" t="inlineStr">
+      <c r="AM5" s="6" t="n"/>
+      <c r="AN5" s="6" t="n"/>
+      <c r="AO5" s="6" t="n"/>
+      <c r="AP5" s="6" t="n"/>
+      <c r="AQ5" s="6" t="n"/>
+      <c r="AR5" s="4" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="AS5" s="4" t="n">
+      <c r="AS5" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AT5" s="4" t="n">
+      <c r="AT5" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AU5" s="4" t="n">
+      <c r="AU5" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AV5" s="4" t="n">
+      <c r="AV5" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AW5" s="4" t="n">
+      <c r="AW5" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AX5" s="4" t="n">
+      <c r="AX5" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AY5" s="4" t="n">
+      <c r="AY5" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AZ5" s="4" t="n">
+      <c r="AZ5" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="BA5" s="4" t="n">
+      <c r="BA5" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="BB5" s="4" t="n">
+      <c r="BB5" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="BC5" s="4" t="n">
+      <c r="BC5" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BD5" s="4" t="n">
+      <c r="BD5" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="BF5" s="2" t="n"/>
-      <c r="BG5" s="2" t="n"/>
-      <c r="BH5" s="2" t="n"/>
+      <c r="BF5" s="3" t="n"/>
+      <c r="BG5" s="3" t="n"/>
+      <c r="BH5" s="3" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="3" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q6" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="S6" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="T6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="n"/>
-      <c r="AA6" s="5" t="n"/>
-      <c r="AB6" s="4" t="n">
+      <c r="Z6" s="6" t="n"/>
+      <c r="AA6" s="6" t="n"/>
+      <c r="AB6" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AD6" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AE6" s="4" t="n">
+      <c r="AE6" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AF6" s="4" t="n">
+      <c r="AF6" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AG6" s="4" t="n">
+      <c r="AG6" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AH6" s="4" t="n">
+      <c r="AH6" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AI6" s="4" t="n">
+      <c r="AI6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ6" s="4" t="n">
+      <c r="AJ6" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AK6" s="4" t="n">
+      <c r="AK6" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL6" s="4" t="n">
+      <c r="AL6" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AM6" s="4" t="n">
+      <c r="AM6" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AN6" s="5" t="n"/>
-      <c r="AO6" s="5" t="n"/>
-      <c r="AP6" s="5" t="n"/>
-      <c r="AQ6" s="5" t="n"/>
-      <c r="AR6" s="3" t="inlineStr">
+      <c r="AN6" s="6" t="n"/>
+      <c r="AO6" s="6" t="n"/>
+      <c r="AP6" s="6" t="n"/>
+      <c r="AQ6" s="6" t="n"/>
+      <c r="AR6" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AS6" s="4" t="n">
+      <c r="AS6" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AT6" s="4" t="n">
+      <c r="AT6" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AU6" s="4" t="n">
+      <c r="AU6" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AV6" s="4" t="n">
+      <c r="AV6" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AW6" s="4" t="n">
+      <c r="AW6" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AX6" s="4" t="n">
+      <c r="AX6" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AY6" s="4" t="n">
+      <c r="AY6" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AZ6" s="4" t="n">
+      <c r="AZ6" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="BA6" s="4" t="n">
+      <c r="BA6" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="BB6" s="4" t="n">
+      <c r="BB6" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BC6" s="4" t="n">
+      <c r="BC6" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BD6" s="4" t="n">
+      <c r="BD6" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BE6" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BF6" s="2" t="n"/>
-      <c r="BG6" s="2" t="n"/>
-      <c r="BH6" s="2" t="n"/>
+      <c r="BF6" s="3" t="n"/>
+      <c r="BG6" s="3" t="n"/>
+      <c r="BH6" s="3" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="Q7" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="R7" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="S7" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="T7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="V7" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="n"/>
-      <c r="AA7" s="4" t="n">
+      <c r="Z7" s="6" t="n"/>
+      <c r="AA7" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AD7" s="4" t="n">
+      <c r="AD7" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AE7" s="4" t="n">
+      <c r="AE7" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AF7" s="4" t="n">
+      <c r="AF7" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AG7" s="4" t="n">
+      <c r="AG7" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AH7" s="4" t="n">
+      <c r="AH7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AI7" s="4" t="n">
+      <c r="AI7" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AJ7" s="4" t="n">
+      <c r="AJ7" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AK7" s="4" t="n">
+      <c r="AK7" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AL7" s="4" t="n">
+      <c r="AL7" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AM7" s="4" t="n">
+      <c r="AM7" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AN7" s="5" t="n"/>
-      <c r="AO7" s="5" t="n"/>
-      <c r="AP7" s="5" t="n"/>
-      <c r="AQ7" s="5" t="n"/>
-      <c r="AR7" s="3" t="inlineStr">
+      <c r="AN7" s="6" t="n"/>
+      <c r="AO7" s="6" t="n"/>
+      <c r="AP7" s="6" t="n"/>
+      <c r="AQ7" s="6" t="n"/>
+      <c r="AR7" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AS7" s="4" t="n">
+      <c r="AS7" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AT7" s="4" t="n">
+      <c r="AT7" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AU7" s="4" t="n">
+      <c r="AU7" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AV7" s="4" t="n">
+      <c r="AV7" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AW7" s="4" t="n">
+      <c r="AW7" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AX7" s="4" t="n">
+      <c r="AX7" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AY7" s="4" t="n">
+      <c r="AY7" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AZ7" s="4" t="n">
+      <c r="AZ7" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="BA7" s="4" t="n">
+      <c r="BA7" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BB7" s="4" t="n">
+      <c r="BB7" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BC7" s="4" t="n">
+      <c r="BC7" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BD7" s="4" t="n">
+      <c r="BD7" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="BF7" s="2" t="n"/>
-      <c r="BG7" s="2" t="n"/>
-      <c r="BH7" s="2" t="n"/>
+      <c r="BF7" s="3" t="n"/>
+      <c r="BG7" s="3" t="n"/>
+      <c r="BH7" s="3" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="Q8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S8" s="4" t="n">
+      <c r="S8" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="V8" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Z8" s="5" t="n"/>
-      <c r="AA8" s="4" t="n">
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AD8" s="4" t="n">
+      <c r="AD8" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AE8" s="4" t="n">
+      <c r="AE8" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AF8" s="4" t="n">
+      <c r="AF8" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AG8" s="4" t="n">
+      <c r="AG8" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AH8" s="4" t="n">
+      <c r="AH8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AI8" s="4" t="n">
+      <c r="AI8" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AJ8" s="4" t="n">
+      <c r="AJ8" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AK8" s="4" t="n">
+      <c r="AK8" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AL8" s="4" t="n">
+      <c r="AL8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AM8" s="4" t="n">
+      <c r="AM8" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AN8" s="5" t="n"/>
-      <c r="AO8" s="5" t="n"/>
-      <c r="AP8" s="5" t="n"/>
-      <c r="AQ8" s="5" t="n"/>
-      <c r="AR8" s="3" t="inlineStr">
+      <c r="AN8" s="6" t="n"/>
+      <c r="AO8" s="6" t="n"/>
+      <c r="AP8" s="6" t="n"/>
+      <c r="AQ8" s="6" t="n"/>
+      <c r="AR8" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AS8" s="4" t="n">
+      <c r="AS8" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AT8" s="4" t="n">
+      <c r="AT8" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AU8" s="4" t="n">
+      <c r="AU8" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AV8" s="4" t="n">
+      <c r="AV8" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AW8" s="4" t="n">
+      <c r="AW8" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AX8" s="4" t="n">
+      <c r="AX8" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AY8" s="4" t="n">
+      <c r="AY8" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AZ8" s="4" t="n">
+      <c r="AZ8" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="BA8" s="4" t="n">
+      <c r="BA8" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BB8" s="4" t="n">
+      <c r="BB8" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BC8" s="4" t="n">
+      <c r="BC8" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BD8" s="4" t="n">
+      <c r="BD8" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="BF8" s="2" t="n"/>
-      <c r="BG8" s="2" t="n"/>
-      <c r="BH8" s="2" t="n"/>
+      <c r="BF8" s="3" t="n"/>
+      <c r="BG8" s="3" t="n"/>
+      <c r="BH8" s="3" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="3" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="M9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="P9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="Q9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="R9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="S9" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="V9" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Z9" s="5" t="n"/>
-      <c r="AA9" s="4" t="n">
+      <c r="Z9" s="6" t="n"/>
+      <c r="AA9" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AD9" s="4" t="n">
+      <c r="AD9" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AE9" s="4" t="n">
+      <c r="AE9" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AF9" s="4" t="n">
+      <c r="AF9" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AG9" s="4" t="n">
+      <c r="AG9" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AH9" s="4" t="n">
+      <c r="AH9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AI9" s="4" t="n">
+      <c r="AI9" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AJ9" s="4" t="n">
+      <c r="AJ9" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AK9" s="4" t="n">
+      <c r="AK9" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AL9" s="4" t="n">
+      <c r="AL9" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AM9" s="4" t="n">
+      <c r="AM9" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AN9" s="4" t="n">
+      <c r="AN9" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AO9" s="5" t="n"/>
-      <c r="AP9" s="5" t="n"/>
-      <c r="AQ9" s="5" t="n"/>
-      <c r="AR9" s="3" t="inlineStr">
+      <c r="AO9" s="6" t="n"/>
+      <c r="AP9" s="6" t="n"/>
+      <c r="AQ9" s="6" t="n"/>
+      <c r="AR9" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="AS9" s="4" t="n">
+      <c r="AS9" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AT9" s="4" t="n">
+      <c r="AT9" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AU9" s="4" t="n">
+      <c r="AU9" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AV9" s="4" t="n">
+      <c r="AV9" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AW9" s="4" t="n">
+      <c r="AW9" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AX9" s="4" t="n">
+      <c r="AX9" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AY9" s="4" t="n">
+      <c r="AY9" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AZ9" s="4" t="n">
+      <c r="AZ9" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BA9" s="4" t="n">
+      <c r="BA9" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BB9" s="4" t="n">
+      <c r="BB9" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BC9" s="4" t="n">
+      <c r="BC9" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BD9" s="4" t="n">
+      <c r="BD9" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="BF9" s="2" t="n"/>
-      <c r="BG9" s="2" t="n"/>
-      <c r="BH9" s="2" t="n"/>
+      <c r="BF9" s="3" t="n"/>
+      <c r="BG9" s="3" t="n"/>
+      <c r="BH9" s="3" t="n"/>
     </row>
-    <row r="10" ht="6" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="3" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="P10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="Q10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="R10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S10" s="4" t="n">
+      <c r="S10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="T10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="V10" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="n">
+      <c r="Z10" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AA10" s="4" t="n">
+      <c r="AA10" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AB10" s="4" t="n">
+      <c r="AB10" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AC10" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AD10" s="4" t="n">
+      <c r="AD10" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AE10" s="4" t="n">
+      <c r="AE10" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AF10" s="4" t="n">
+      <c r="AF10" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AG10" s="4" t="n">
+      <c r="AG10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AH10" s="4" t="n">
+      <c r="AH10" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AI10" s="4" t="n">
+      <c r="AI10" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AJ10" s="4" t="n">
+      <c r="AJ10" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AK10" s="4" t="n">
+      <c r="AK10" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AL10" s="4" t="n">
+      <c r="AL10" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AM10" s="4" t="n">
+      <c r="AM10" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AN10" s="4" t="n">
+      <c r="AN10" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AO10" s="5" t="n"/>
-      <c r="AP10" s="5" t="n"/>
-      <c r="AQ10" s="5" t="n"/>
-      <c r="AR10" s="3" t="inlineStr">
+      <c r="AO10" s="6" t="n"/>
+      <c r="AP10" s="6" t="n"/>
+      <c r="AQ10" s="6" t="n"/>
+      <c r="AR10" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="AS10" s="4" t="n">
+      <c r="AS10" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AT10" s="4" t="n">
+      <c r="AT10" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AU10" s="4" t="n">
+      <c r="AU10" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AV10" s="4" t="n">
+      <c r="AV10" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AW10" s="4" t="n">
+      <c r="AW10" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AX10" s="4" t="n">
+      <c r="AX10" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AY10" s="4" t="n">
+      <c r="AY10" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AZ10" s="4" t="n">
+      <c r="AZ10" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BA10" s="4" t="n">
+      <c r="BA10" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BB10" s="4" t="n">
+      <c r="BB10" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BC10" s="4" t="n">
+      <c r="BC10" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BD10" s="4" t="n">
+      <c r="BD10" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BE10" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="BF10" s="2" t="n"/>
-      <c r="BG10" s="2" t="n"/>
-      <c r="BH10" s="2" t="n"/>
+      <c r="BF10" s="3" t="n"/>
+      <c r="BG10" s="3" t="n"/>
+      <c r="BH10" s="3" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="3" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="K11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="M11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="O11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="P11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="Q11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="R11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="S11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="V11" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="Z11" s="4" t="n">
+      <c r="Z11" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AA11" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AD11" s="4" t="n">
+      <c r="AD11" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AE11" s="4" t="n">
+      <c r="AE11" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AF11" s="4" t="n">
+      <c r="AF11" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AG11" s="4" t="n">
+      <c r="AG11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AH11" s="4" t="n">
+      <c r="AH11" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AI11" s="4" t="n">
+      <c r="AI11" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AJ11" s="4" t="n">
+      <c r="AJ11" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AK11" s="4" t="n">
+      <c r="AK11" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AL11" s="4" t="n">
+      <c r="AL11" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AM11" s="4" t="n">
+      <c r="AM11" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AN11" s="4" t="n">
+      <c r="AN11" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AO11" s="4" t="n">
+      <c r="AO11" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AP11" s="5" t="n"/>
-      <c r="AQ11" s="5" t="n"/>
-      <c r="AR11" s="3" t="inlineStr">
+      <c r="AP11" s="6" t="n"/>
+      <c r="AQ11" s="6" t="n"/>
+      <c r="AR11" s="4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AS11" s="4" t="n">
+      <c r="AS11" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AT11" s="4" t="n">
+      <c r="AT11" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AU11" s="4" t="n">
+      <c r="AU11" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AV11" s="4" t="n">
+      <c r="AV11" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AW11" s="4" t="n">
+      <c r="AW11" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AX11" s="4" t="n">
+      <c r="AX11" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AY11" s="4" t="n">
+      <c r="AY11" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AZ11" s="4" t="n">
+      <c r="AZ11" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BA11" s="4" t="n">
+      <c r="BA11" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BB11" s="4" t="n">
+      <c r="BB11" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BC11" s="4" t="n">
+      <c r="BC11" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BD11" s="4" t="n">
+      <c r="BD11" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BE11" s="4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="BF11" s="2" t="n"/>
-      <c r="BG11" s="2" t="n"/>
-      <c r="BH11" s="2" t="n"/>
+      <c r="BF11" s="3" t="n"/>
+      <c r="BG11" s="3" t="n"/>
+      <c r="BH11" s="3" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="K12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="O12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="P12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="Q12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="R12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S12" s="4" t="n">
+      <c r="S12" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="U12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V12" s="4" t="n">
+      <c r="V12" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-      <c r="Y12" s="3" t="inlineStr">
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="Z12" s="4" t="n">
+      <c r="Z12" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AA12" s="4" t="n">
+      <c r="AA12" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AB12" s="4" t="n">
+      <c r="AB12" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AC12" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AD12" s="4" t="n">
+      <c r="AD12" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AE12" s="4" t="n">
+      <c r="AE12" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AF12" s="4" t="n">
+      <c r="AF12" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AG12" s="4" t="n">
+      <c r="AG12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AH12" s="4" t="n">
+      <c r="AH12" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AI12" s="4" t="n">
+      <c r="AI12" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AJ12" s="4" t="n">
+      <c r="AJ12" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AK12" s="4" t="n">
+      <c r="AK12" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AL12" s="4" t="n">
+      <c r="AL12" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AM12" s="4" t="n">
+      <c r="AM12" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AN12" s="4" t="n">
+      <c r="AN12" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AO12" s="4" t="n">
+      <c r="AO12" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AP12" s="4" t="n">
+      <c r="AP12" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AQ12" s="5" t="n"/>
-      <c r="AR12" s="3" t="inlineStr">
+      <c r="AQ12" s="6" t="n"/>
+      <c r="AR12" s="4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="AS12" s="4" t="n">
+      <c r="AS12" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AT12" s="4" t="n">
+      <c r="AT12" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AU12" s="4" t="n">
+      <c r="AU12" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AV12" s="4" t="n">
+      <c r="AV12" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AW12" s="4" t="n">
+      <c r="AW12" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AX12" s="4" t="n">
+      <c r="AX12" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AY12" s="4" t="n">
+      <c r="AY12" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AZ12" s="4" t="n">
+      <c r="AZ12" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BA12" s="4" t="n">
+      <c r="BA12" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BB12" s="4" t="n">
+      <c r="BB12" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BC12" s="4" t="n">
+      <c r="BC12" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="BD12" s="4" t="n">
+      <c r="BD12" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BE12" s="4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="BF12" s="2" t="n"/>
-      <c r="BG12" s="2" t="n"/>
-      <c r="BH12" s="2" t="n"/>
+      <c r="BF12" s="3" t="n"/>
+      <c r="BG12" s="3" t="n"/>
+      <c r="BH12" s="3" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1"/>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="3" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="M14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="O14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="P14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="4" t="n">
+      <c r="T14" s="6" t="n"/>
+      <c r="U14" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="V14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W14" s="4" t="n">
+      <c r="W14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="X14" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="Y14" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z14" s="4" t="n">
+      <c r="Z14" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA14" s="4" t="n">
+      <c r="AA14" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB14" s="5" t="n"/>
-      <c r="AC14" s="5" t="n"/>
-      <c r="AD14" s="5" t="n"/>
-      <c r="AE14" s="3" t="inlineStr">
+      <c r="AB14" s="6" t="n"/>
+      <c r="AC14" s="6" t="n"/>
+      <c r="AD14" s="6" t="n"/>
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="AF14" s="5" t="n"/>
-      <c r="AG14" s="4" t="n">
+      <c r="AF14" s="6" t="n"/>
+      <c r="AG14" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AH14" s="4" t="n">
+      <c r="AH14" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AI14" s="4" t="n">
+      <c r="AI14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ14" s="4" t="n">
+      <c r="AJ14" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AK14" s="4" t="n">
+      <c r="AK14" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL14" s="4" t="n">
+      <c r="AL14" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AM14" s="4" t="n">
+      <c r="AM14" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AN14" s="5" t="n"/>
-      <c r="AO14" s="5" t="n"/>
-      <c r="AP14" s="5" t="n"/>
-      <c r="AQ14" s="5" t="n"/>
-      <c r="AR14" s="3" t="inlineStr">
+      <c r="AN14" s="6" t="n"/>
+      <c r="AO14" s="6" t="n"/>
+      <c r="AP14" s="6" t="n"/>
+      <c r="AQ14" s="6" t="n"/>
+      <c r="AR14" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="AS14" s="4" t="n">
+      <c r="AS14" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AT14" s="4" t="n">
+      <c r="AT14" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AU14" s="4" t="n">
+      <c r="AU14" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AV14" s="4" t="n">
+      <c r="AV14" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AW14" s="4" t="n">
+      <c r="AW14" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AX14" s="4" t="n">
+      <c r="AX14" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AY14" s="4" t="n">
+      <c r="AY14" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AZ14" s="4" t="n">
+      <c r="AZ14" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="BA14" s="4" t="n">
+      <c r="BA14" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="BB14" s="4" t="n">
+      <c r="BB14" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="BC14" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="BD14" s="2" t="n"/>
-      <c r="BE14" s="2" t="n"/>
-      <c r="BF14" s="2" t="n"/>
-      <c r="BG14" s="2" t="n"/>
-      <c r="BH14" s="2" t="n"/>
+      <c r="BD14" s="3" t="n"/>
+      <c r="BE14" s="3" t="n"/>
+      <c r="BF14" s="3" t="n"/>
+      <c r="BG14" s="3" t="n"/>
+      <c r="BH14" s="3" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="3" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="K15" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="M15" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="O15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="P15" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="Q15" s="6" t="n"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="4" t="n">
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="V15" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="W15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="X15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="Y15" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z15" s="4" t="n">
+      <c r="Z15" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AA15" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB15" s="5" t="n"/>
-      <c r="AC15" s="5" t="n"/>
-      <c r="AD15" s="5" t="n"/>
-      <c r="AE15" s="3" t="inlineStr">
+      <c r="AB15" s="6" t="n"/>
+      <c r="AC15" s="6" t="n"/>
+      <c r="AD15" s="6" t="n"/>
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="AF15" s="5" t="n"/>
-      <c r="AG15" s="4" t="n">
+      <c r="AF15" s="6" t="n"/>
+      <c r="AG15" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AH15" s="4" t="n">
+      <c r="AH15" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AI15" s="4" t="n">
+      <c r="AI15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ15" s="4" t="n">
+      <c r="AJ15" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AK15" s="4" t="n">
+      <c r="AK15" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL15" s="4" t="n">
+      <c r="AL15" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AM15" s="4" t="n">
+      <c r="AM15" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AN15" s="5" t="n"/>
-      <c r="AO15" s="5" t="n"/>
-      <c r="AP15" s="5" t="n"/>
-      <c r="AQ15" s="5" t="n"/>
-      <c r="AR15" s="3" t="inlineStr">
+      <c r="AN15" s="6" t="n"/>
+      <c r="AO15" s="6" t="n"/>
+      <c r="AP15" s="6" t="n"/>
+      <c r="AQ15" s="6" t="n"/>
+      <c r="AR15" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="AS15" s="4" t="n">
+      <c r="AS15" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AT15" s="4" t="n">
+      <c r="AT15" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AU15" s="4" t="n">
+      <c r="AU15" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AV15" s="4" t="n">
+      <c r="AV15" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AW15" s="4" t="n">
+      <c r="AW15" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AX15" s="4" t="n">
+      <c r="AX15" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AY15" s="4" t="n">
+      <c r="AY15" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AZ15" s="4" t="n">
+      <c r="AZ15" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="BA15" s="4" t="n">
+      <c r="BA15" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="BB15" s="4" t="n">
+      <c r="BB15" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="BC15" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="BD15" s="2" t="n"/>
-      <c r="BE15" s="2" t="n"/>
-      <c r="BF15" s="2" t="n"/>
-      <c r="BG15" s="2" t="n"/>
-      <c r="BH15" s="2" t="n"/>
+      <c r="BD15" s="3" t="n"/>
+      <c r="BE15" s="3" t="n"/>
+      <c r="BF15" s="3" t="n"/>
+      <c r="BG15" s="3" t="n"/>
+      <c r="BH15" s="3" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="3" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="K16" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="M16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="O16" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="P16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="4" t="n">
+      <c r="T16" s="6" t="n"/>
+      <c r="U16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V16" s="4" t="n">
+      <c r="V16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W16" s="4" t="n">
+      <c r="W16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X16" s="4" t="n">
+      <c r="X16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="Y16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z16" s="4" t="n">
+      <c r="Z16" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AA16" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB16" s="4" t="n">
+      <c r="AB16" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AC16" s="5" t="n"/>
-      <c r="AD16" s="5" t="n"/>
-      <c r="AE16" s="3" t="inlineStr">
+      <c r="AC16" s="6" t="n"/>
+      <c r="AD16" s="6" t="n"/>
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="AF16" s="5" t="n"/>
-      <c r="AG16" s="4" t="n">
+      <c r="AF16" s="6" t="n"/>
+      <c r="AG16" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AH16" s="4" t="n">
+      <c r="AH16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AI16" s="4" t="n">
+      <c r="AI16" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AJ16" s="4" t="n">
+      <c r="AJ16" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AK16" s="4" t="n">
+      <c r="AK16" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AL16" s="4" t="n">
+      <c r="AL16" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AM16" s="4" t="n">
+      <c r="AM16" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AN16" s="4" t="n">
+      <c r="AN16" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AO16" s="5" t="n"/>
-      <c r="AP16" s="5" t="n"/>
-      <c r="AQ16" s="5" t="n"/>
-      <c r="AR16" s="3" t="inlineStr">
+      <c r="AO16" s="6" t="n"/>
+      <c r="AP16" s="6" t="n"/>
+      <c r="AQ16" s="6" t="n"/>
+      <c r="AR16" s="4" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="AS16" s="4" t="n">
+      <c r="AS16" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AT16" s="4" t="n">
+      <c r="AT16" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AU16" s="4" t="n">
+      <c r="AU16" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AV16" s="4" t="n">
+      <c r="AV16" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AW16" s="4" t="n">
+      <c r="AW16" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AX16" s="4" t="n">
+      <c r="AX16" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AY16" s="4" t="n">
+      <c r="AY16" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AZ16" s="4" t="n">
+      <c r="AZ16" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BA16" s="4" t="n">
+      <c r="BA16" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BB16" s="4" t="n">
+      <c r="BB16" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BC16" s="3" t="inlineStr">
+      <c r="BC16" s="4" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="BD16" s="2" t="n"/>
-      <c r="BE16" s="2" t="n"/>
-      <c r="BF16" s="2" t="n"/>
-      <c r="BG16" s="2" t="n"/>
-      <c r="BH16" s="2" t="n"/>
+      <c r="BD16" s="3" t="n"/>
+      <c r="BE16" s="3" t="n"/>
+      <c r="BF16" s="3" t="n"/>
+      <c r="BG16" s="3" t="n"/>
+      <c r="BH16" s="3" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="3" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="K17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="M17" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="O17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="P17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="4" t="n">
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="V17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="W17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="X17" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y17" s="4" t="n">
+      <c r="Y17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z17" s="4" t="n">
+      <c r="Z17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AA17" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB17" s="4" t="n">
+      <c r="AB17" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AC17" s="5" t="n"/>
-      <c r="AD17" s="5" t="n"/>
-      <c r="AE17" s="3" t="inlineStr">
+      <c r="AC17" s="6" t="n"/>
+      <c r="AD17" s="6" t="n"/>
+      <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="AF17" s="5" t="n"/>
-      <c r="AG17" s="4" t="n">
+      <c r="AF17" s="6" t="n"/>
+      <c r="AG17" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AH17" s="4" t="n">
+      <c r="AH17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AI17" s="4" t="n">
+      <c r="AI17" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AJ17" s="4" t="n">
+      <c r="AJ17" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AK17" s="4" t="n">
+      <c r="AK17" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AL17" s="4" t="n">
+      <c r="AL17" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AM17" s="4" t="n">
+      <c r="AM17" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AN17" s="4" t="n">
+      <c r="AN17" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AO17" s="5" t="n"/>
-      <c r="AP17" s="5" t="n"/>
-      <c r="AQ17" s="5" t="n"/>
-      <c r="AR17" s="3" t="inlineStr">
+      <c r="AO17" s="6" t="n"/>
+      <c r="AP17" s="6" t="n"/>
+      <c r="AQ17" s="6" t="n"/>
+      <c r="AR17" s="4" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="AS17" s="4" t="n">
+      <c r="AS17" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AT17" s="4" t="n">
+      <c r="AT17" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AU17" s="4" t="n">
+      <c r="AU17" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AV17" s="4" t="n">
+      <c r="AV17" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AW17" s="4" t="n">
+      <c r="AW17" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AX17" s="4" t="n">
+      <c r="AX17" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AY17" s="4" t="n">
+      <c r="AY17" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AZ17" s="4" t="n">
+      <c r="AZ17" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="BA17" s="4" t="n">
+      <c r="BA17" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BB17" s="4" t="n">
+      <c r="BB17" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BC17" s="3" t="inlineStr">
+      <c r="BC17" s="4" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="BD17" s="2" t="n"/>
-      <c r="BE17" s="2" t="n"/>
-      <c r="BF17" s="2" t="n"/>
-      <c r="BG17" s="2" t="n"/>
-      <c r="BH17" s="2" t="n"/>
+      <c r="BD17" s="3" t="n"/>
+      <c r="BE17" s="3" t="n"/>
+      <c r="BF17" s="3" t="n"/>
+      <c r="BG17" s="3" t="n"/>
+      <c r="BH17" s="3" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="3" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="K18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="M18" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="O18" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="P18" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="T18" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="U18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="V18" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="W18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="X18" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" s="4" t="n">
+      <c r="Y18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="Z18" s="4" t="n">
+      <c r="Z18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AA18" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AB18" s="4" t="n">
+      <c r="AB18" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AC18" s="5" t="n"/>
-      <c r="AD18" s="5" t="n"/>
-      <c r="AE18" s="3" t="inlineStr">
+      <c r="AC18" s="6" t="n"/>
+      <c r="AD18" s="6" t="n"/>
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="AF18" s="5" t="n"/>
-      <c r="AG18" s="4" t="n">
+      <c r="AF18" s="6" t="n"/>
+      <c r="AG18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AH18" s="4" t="n">
+      <c r="AH18" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AI18" s="4" t="n">
+      <c r="AI18" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AJ18" s="4" t="n">
+      <c r="AJ18" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AK18" s="4" t="n">
+      <c r="AK18" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AL18" s="4" t="n">
+      <c r="AL18" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AM18" s="4" t="n">
+      <c r="AM18" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AN18" s="4" t="n">
+      <c r="AN18" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AO18" s="4" t="n">
+      <c r="AO18" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AP18" s="5" t="n"/>
-      <c r="AQ18" s="5" t="n"/>
-      <c r="AR18" s="3" t="inlineStr">
+      <c r="AP18" s="6" t="n"/>
+      <c r="AQ18" s="6" t="n"/>
+      <c r="AR18" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="AS18" s="4" t="n">
+      <c r="AS18" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AT18" s="4" t="n">
+      <c r="AT18" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AU18" s="4" t="n">
+      <c r="AU18" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AV18" s="4" t="n">
+      <c r="AV18" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AW18" s="4" t="n">
+      <c r="AW18" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AX18" s="4" t="n">
+      <c r="AX18" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AY18" s="4" t="n">
+      <c r="AY18" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AZ18" s="4" t="n">
+      <c r="AZ18" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BA18" s="4" t="n">
+      <c r="BA18" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BB18" s="4" t="n">
+      <c r="BB18" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BC18" s="3" t="inlineStr">
+      <c r="BC18" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="BD18" s="2" t="n"/>
-      <c r="BE18" s="2" t="n"/>
-      <c r="BF18" s="2" t="n"/>
-      <c r="BG18" s="2" t="n"/>
-      <c r="BH18" s="2" t="n"/>
+      <c r="BD18" s="3" t="n"/>
+      <c r="BE18" s="3" t="n"/>
+      <c r="BF18" s="3" t="n"/>
+      <c r="BG18" s="3" t="n"/>
+      <c r="BH18" s="3" t="n"/>
     </row>
-    <row r="19" ht="6" customHeight="1">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="3" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="K19" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="M19" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="O19" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="3" t="inlineStr">
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="T19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U19" s="4" t="n">
+      <c r="U19" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="V19" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W19" s="4" t="n">
+      <c r="W19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="X19" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y19" s="4" t="n">
+      <c r="Y19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z19" s="4" t="n">
+      <c r="Z19" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA19" s="4" t="n">
+      <c r="AA19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB19" s="4" t="n">
+      <c r="AB19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AC19" s="5" t="n"/>
-      <c r="AD19" s="5" t="n"/>
-      <c r="AE19" s="3" t="inlineStr">
+      <c r="AC19" s="6" t="n"/>
+      <c r="AD19" s="6" t="n"/>
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AF19" s="5" t="n"/>
-      <c r="AG19" s="4" t="n">
+      <c r="AF19" s="6" t="n"/>
+      <c r="AG19" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AH19" s="4" t="n">
+      <c r="AH19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AI19" s="4" t="n">
+      <c r="AI19" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AJ19" s="4" t="n">
+      <c r="AJ19" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AK19" s="4" t="n">
+      <c r="AK19" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AL19" s="4" t="n">
+      <c r="AL19" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AM19" s="4" t="n">
+      <c r="AM19" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AN19" s="4" t="n">
+      <c r="AN19" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AO19" s="4" t="n">
+      <c r="AO19" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AP19" s="5" t="n"/>
-      <c r="AQ19" s="5" t="n"/>
-      <c r="AR19" s="3" t="inlineStr">
+      <c r="AP19" s="6" t="n"/>
+      <c r="AQ19" s="6" t="n"/>
+      <c r="AR19" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AS19" s="4" t="n">
+      <c r="AS19" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AT19" s="4" t="n">
+      <c r="AT19" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AU19" s="4" t="n">
+      <c r="AU19" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AV19" s="4" t="n">
+      <c r="AV19" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AW19" s="4" t="n">
+      <c r="AW19" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AX19" s="4" t="n">
+      <c r="AX19" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AY19" s="4" t="n">
+      <c r="AY19" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AZ19" s="4" t="n">
+      <c r="AZ19" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="BA19" s="4" t="n">
+      <c r="BA19" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BB19" s="4" t="n">
+      <c r="BB19" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BC19" s="3" t="inlineStr">
+      <c r="BC19" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="BD19" s="2" t="n"/>
-      <c r="BE19" s="2" t="n"/>
-      <c r="BF19" s="2" t="n"/>
-      <c r="BG19" s="2" t="n"/>
-      <c r="BH19" s="2" t="n"/>
+      <c r="BD19" s="3" t="n"/>
+      <c r="BE19" s="3" t="n"/>
+      <c r="BF19" s="3" t="n"/>
+      <c r="BG19" s="3" t="n"/>
+      <c r="BH19" s="3" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="3" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="K20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="O20" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="T20" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U20" s="4" t="n">
+      <c r="U20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="V20" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="W20" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="X20" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y20" s="4" t="n">
+      <c r="Y20" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z20" s="4" t="n">
+      <c r="Z20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA20" s="4" t="n">
+      <c r="AA20" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB20" s="4" t="n">
+      <c r="AB20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AC20" s="4" t="n">
+      <c r="AC20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AD20" s="5" t="n"/>
-      <c r="AE20" s="3" t="inlineStr">
+      <c r="AD20" s="6" t="n"/>
+      <c r="AE20" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="n">
+      <c r="AF20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AG20" s="4" t="n">
+      <c r="AG20" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AH20" s="4" t="n">
+      <c r="AH20" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AI20" s="4" t="n">
+      <c r="AI20" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AJ20" s="4" t="n">
+      <c r="AJ20" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AK20" s="4" t="n">
+      <c r="AK20" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AL20" s="4" t="n">
+      <c r="AL20" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AM20" s="4" t="n">
+      <c r="AM20" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AN20" s="4" t="n">
+      <c r="AN20" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AO20" s="4" t="n">
+      <c r="AO20" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AP20" s="5" t="n"/>
-      <c r="AQ20" s="5" t="n"/>
-      <c r="AR20" s="3" t="inlineStr">
+      <c r="AP20" s="6" t="n"/>
+      <c r="AQ20" s="6" t="n"/>
+      <c r="AR20" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AS20" s="4" t="n">
+      <c r="AS20" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AT20" s="4" t="n">
+      <c r="AT20" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AU20" s="4" t="n">
+      <c r="AU20" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AV20" s="4" t="n">
+      <c r="AV20" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AW20" s="4" t="n">
+      <c r="AW20" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AX20" s="4" t="n">
+      <c r="AX20" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AY20" s="4" t="n">
+      <c r="AY20" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AZ20" s="4" t="n">
+      <c r="AZ20" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BA20" s="4" t="n">
+      <c r="BA20" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BB20" s="5" t="n"/>
-      <c r="BC20" s="3" t="inlineStr">
+      <c r="BB20" s="6" t="n"/>
+      <c r="BC20" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BD20" s="2" t="n"/>
-      <c r="BE20" s="2" t="n"/>
-      <c r="BF20" s="2" t="n"/>
-      <c r="BG20" s="2" t="n"/>
-      <c r="BH20" s="2" t="n"/>
+      <c r="BD20" s="3" t="n"/>
+      <c r="BE20" s="3" t="n"/>
+      <c r="BF20" s="3" t="n"/>
+      <c r="BG20" s="3" t="n"/>
+      <c r="BH20" s="3" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="3" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="K21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="M21" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="O21" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="T21" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U21" s="4" t="n">
+      <c r="U21" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="V21" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W21" s="4" t="n">
+      <c r="W21" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="X21" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y21" s="4" t="n">
+      <c r="Y21" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z21" s="4" t="n">
+      <c r="Z21" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA21" s="4" t="n">
+      <c r="AA21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB21" s="4" t="n">
+      <c r="AB21" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AC21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AD21" s="5" t="n"/>
-      <c r="AE21" s="3" t="inlineStr">
+      <c r="AD21" s="6" t="n"/>
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="n">
+      <c r="AF21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AG21" s="4" t="n">
+      <c r="AG21" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AH21" s="4" t="n">
+      <c r="AH21" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AI21" s="4" t="n">
+      <c r="AI21" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AJ21" s="4" t="n">
+      <c r="AJ21" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AK21" s="4" t="n">
+      <c r="AK21" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AL21" s="4" t="n">
+      <c r="AL21" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AM21" s="4" t="n">
+      <c r="AM21" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AN21" s="4" t="n">
+      <c r="AN21" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AO21" s="4" t="n">
+      <c r="AO21" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AP21" s="5" t="n"/>
-      <c r="AQ21" s="5" t="n"/>
-      <c r="AR21" s="3" t="inlineStr">
+      <c r="AP21" s="6" t="n"/>
+      <c r="AQ21" s="6" t="n"/>
+      <c r="AR21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AS21" s="4" t="n">
+      <c r="AS21" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AT21" s="4" t="n">
+      <c r="AT21" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AU21" s="4" t="n">
+      <c r="AU21" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AV21" s="4" t="n">
+      <c r="AV21" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AW21" s="4" t="n">
+      <c r="AW21" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AX21" s="4" t="n">
+      <c r="AX21" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AY21" s="4" t="n">
+      <c r="AY21" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AZ21" s="4" t="n">
+      <c r="AZ21" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BA21" s="4" t="n">
+      <c r="BA21" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BB21" s="5" t="n"/>
-      <c r="BC21" s="3" t="inlineStr">
+      <c r="BB21" s="6" t="n"/>
+      <c r="BC21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="BD21" s="2" t="n"/>
-      <c r="BE21" s="2" t="n"/>
-      <c r="BF21" s="2" t="n"/>
-      <c r="BG21" s="2" t="n"/>
-      <c r="BH21" s="2" t="n"/>
+      <c r="BD21" s="3" t="n"/>
+      <c r="BE21" s="3" t="n"/>
+      <c r="BF21" s="3" t="n"/>
+      <c r="BG21" s="3" t="n"/>
+      <c r="BH21" s="3" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="K23" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="P23" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="Q23" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="R23" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="S23" s="4" t="n">
+      <c r="S23" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="T23" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U23" s="4" t="n">
+      <c r="U23" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="V23" s="4" t="n">
+      <c r="V23" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="W23" s="4" t="n">
+      <c r="W23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="X23" s="4" t="n">
+      <c r="X23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="Y23" s="4" t="n">
+      <c r="Y23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="Z23" s="5" t="n"/>
-      <c r="AA23" s="5" t="n"/>
-      <c r="AB23" s="5" t="n"/>
-      <c r="AC23" s="5" t="n"/>
-      <c r="AD23" s="5" t="n"/>
-      <c r="AE23" s="3" t="inlineStr">
+      <c r="Z23" s="6" t="n"/>
+      <c r="AA23" s="6" t="n"/>
+      <c r="AB23" s="6" t="n"/>
+      <c r="AC23" s="6" t="n"/>
+      <c r="AD23" s="6" t="n"/>
+      <c r="AE23" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="AF23" s="5" t="n"/>
-      <c r="AG23" s="5" t="n"/>
-      <c r="AH23" s="4" t="n">
+      <c r="AF23" s="6" t="n"/>
+      <c r="AG23" s="6" t="n"/>
+      <c r="AH23" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AI23" s="4" t="n">
+      <c r="AI23" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AJ23" s="4" t="n">
+      <c r="AJ23" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AK23" s="4" t="n">
+      <c r="AK23" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AL23" s="4" t="n">
+      <c r="AL23" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AM23" s="4" t="n">
+      <c r="AM23" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AN23" s="4" t="n">
+      <c r="AN23" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AO23" s="4" t="n">
+      <c r="AO23" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AP23" s="4" t="n">
+      <c r="AP23" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AQ23" s="4" t="n">
+      <c r="AQ23" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AR23" s="5" t="n"/>
-      <c r="AS23" s="5" t="n"/>
-      <c r="AT23" s="5" t="n"/>
-      <c r="AU23" s="5" t="n"/>
-      <c r="AV23" s="5" t="n"/>
-      <c r="AW23" s="4" t="n">
+      <c r="AR23" s="6" t="n"/>
+      <c r="AS23" s="6" t="n"/>
+      <c r="AT23" s="6" t="n"/>
+      <c r="AU23" s="6" t="n"/>
+      <c r="AV23" s="6" t="n"/>
+      <c r="AW23" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AX23" s="4" t="n">
+      <c r="AX23" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="AY23" s="4" t="n">
+      <c r="AY23" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="AZ23" s="4" t="n">
+      <c r="AZ23" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BA23" s="4" t="n">
+      <c r="BA23" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="BB23" s="4" t="n">
+      <c r="BB23" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="BC23" s="4" t="n">
+      <c r="BC23" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="BD23" s="4" t="n">
+      <c r="BD23" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="BE23" s="4" t="n">
+      <c r="BE23" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="BF23" s="4" t="n">
+      <c r="BF23" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="BG23" s="4" t="n">
+      <c r="BG23" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="BH23" s="3" t="inlineStr">
+      <c r="BH23" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="4" t="n">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="K24" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="P24" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="Q24" s="4" t="n">
+      <c r="Q24" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="R24" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="S24" s="4" t="n">
+      <c r="S24" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="T24" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U24" s="4" t="n">
+      <c r="U24" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="V24" s="4" t="n">
+      <c r="V24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="W24" s="4" t="n">
+      <c r="W24" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="X24" s="4" t="n">
+      <c r="X24" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="Y24" s="4" t="n">
+      <c r="Y24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="Z24" s="4" t="n">
+      <c r="Z24" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AA24" s="4" t="n">
+      <c r="AA24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AB24" s="5" t="n"/>
-      <c r="AC24" s="5" t="n"/>
-      <c r="AD24" s="5" t="n"/>
-      <c r="AE24" s="3" t="inlineStr">
+      <c r="AB24" s="6" t="n"/>
+      <c r="AC24" s="6" t="n"/>
+      <c r="AD24" s="6" t="n"/>
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="n">
+      <c r="AF24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AG24" s="4" t="n">
+      <c r="AG24" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AH24" s="4" t="n">
+      <c r="AH24" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AI24" s="4" t="n">
+      <c r="AI24" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AJ24" s="4" t="n">
+      <c r="AJ24" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AK24" s="4" t="n">
+      <c r="AK24" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AL24" s="4" t="n">
+      <c r="AL24" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AM24" s="4" t="n">
+      <c r="AM24" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AN24" s="4" t="n">
+      <c r="AN24" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AO24" s="4" t="n">
+      <c r="AO24" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AP24" s="4" t="n">
+      <c r="AP24" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AQ24" s="4" t="n">
+      <c r="AQ24" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AR24" s="5" t="n"/>
-      <c r="AS24" s="5" t="n"/>
-      <c r="AT24" s="5" t="n"/>
-      <c r="AU24" s="5" t="n"/>
-      <c r="AV24" s="5" t="n"/>
-      <c r="AW24" s="4" t="n">
+      <c r="AR24" s="6" t="n"/>
+      <c r="AS24" s="6" t="n"/>
+      <c r="AT24" s="6" t="n"/>
+      <c r="AU24" s="6" t="n"/>
+      <c r="AV24" s="6" t="n"/>
+      <c r="AW24" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AX24" s="4" t="n">
+      <c r="AX24" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AY24" s="4" t="n">
+      <c r="AY24" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="AZ24" s="4" t="n">
+      <c r="AZ24" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BA24" s="4" t="n">
+      <c r="BA24" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BB24" s="4" t="n">
+      <c r="BB24" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="BC24" s="4" t="n">
+      <c r="BC24" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="BD24" s="4" t="n">
+      <c r="BD24" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="BE24" s="4" t="n">
+      <c r="BE24" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="BF24" s="4" t="n">
+      <c r="BF24" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="BG24" s="5" t="n"/>
-      <c r="BH24" s="3" t="inlineStr">
+      <c r="BG24" s="6" t="n"/>
+      <c r="BH24" s="4" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="4" t="n">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K25" s="4" t="n">
+      <c r="K25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="P25" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="Q25" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="R25" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="S25" s="4" t="n">
+      <c r="S25" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="U25" s="4" t="n">
+      <c r="U25" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="V25" s="4" t="n">
+      <c r="V25" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="W25" s="4" t="n">
+      <c r="W25" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="X25" s="4" t="n">
+      <c r="X25" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="Y25" s="4" t="n">
+      <c r="Y25" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="Z25" s="4" t="n">
+      <c r="Z25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AA25" s="4" t="n">
+      <c r="AA25" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AB25" s="5" t="n"/>
-      <c r="AC25" s="5" t="n"/>
-      <c r="AD25" s="5" t="n"/>
-      <c r="AE25" s="3" t="inlineStr">
+      <c r="AB25" s="6" t="n"/>
+      <c r="AC25" s="6" t="n"/>
+      <c r="AD25" s="6" t="n"/>
+      <c r="AE25" s="4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="n">
+      <c r="AF25" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AG25" s="4" t="n">
+      <c r="AG25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AH25" s="4" t="n">
+      <c r="AH25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AI25" s="4" t="n">
+      <c r="AI25" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AJ25" s="4" t="n">
+      <c r="AJ25" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AK25" s="4" t="n">
+      <c r="AK25" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AL25" s="4" t="n">
+      <c r="AL25" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AM25" s="4" t="n">
+      <c r="AM25" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AN25" s="4" t="n">
+      <c r="AN25" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AO25" s="4" t="n">
+      <c r="AO25" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AP25" s="4" t="n">
+      <c r="AP25" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AQ25" s="4" t="n">
+      <c r="AQ25" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AR25" s="4" t="n">
+      <c r="AR25" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AS25" s="5" t="n"/>
-      <c r="AT25" s="5" t="n"/>
-      <c r="AU25" s="5" t="n"/>
-      <c r="AV25" s="5" t="n"/>
-      <c r="AW25" s="4" t="n">
+      <c r="AS25" s="6" t="n"/>
+      <c r="AT25" s="6" t="n"/>
+      <c r="AU25" s="6" t="n"/>
+      <c r="AV25" s="6" t="n"/>
+      <c r="AW25" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AX25" s="4" t="n">
+      <c r="AX25" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AY25" s="4" t="n">
+      <c r="AY25" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="AZ25" s="4" t="n">
+      <c r="AZ25" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BA25" s="4" t="n">
+      <c r="BA25" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BB25" s="4" t="n">
+      <c r="BB25" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="BC25" s="4" t="n">
+      <c r="BC25" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="BD25" s="4" t="n">
+      <c r="BD25" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="BE25" s="4" t="n">
+      <c r="BE25" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="BF25" s="5" t="n"/>
-      <c r="BG25" s="5" t="n"/>
-      <c r="BH25" s="3" t="inlineStr">
+      <c r="BF25" s="6" t="n"/>
+      <c r="BG25" s="6" t="n"/>
+      <c r="BH25" s="4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="4" t="n">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K26" s="4" t="n">
+      <c r="K26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="P26" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="Q26" s="4" t="n">
+      <c r="Q26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="R26" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="S26" s="4" t="n">
+      <c r="S26" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="T26" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="U26" s="4" t="n">
+      <c r="U26" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="V26" s="4" t="n">
+      <c r="V26" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="W26" s="4" t="n">
+      <c r="W26" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="X26" s="4" t="n">
+      <c r="X26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="Y26" s="4" t="n">
+      <c r="Y26" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="Z26" s="4" t="n">
+      <c r="Z26" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AA26" s="4" t="n">
+      <c r="AA26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AB26" s="5" t="n"/>
-      <c r="AC26" s="5" t="n"/>
-      <c r="AD26" s="5" t="n"/>
-      <c r="AE26" s="3" t="inlineStr">
+      <c r="AB26" s="6" t="n"/>
+      <c r="AC26" s="6" t="n"/>
+      <c r="AD26" s="6" t="n"/>
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="n">
+      <c r="AF26" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AG26" s="4" t="n">
+      <c r="AG26" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AH26" s="4" t="n">
+      <c r="AH26" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AI26" s="4" t="n">
+      <c r="AI26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AJ26" s="4" t="n">
+      <c r="AJ26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AK26" s="4" t="n">
+      <c r="AK26" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AL26" s="4" t="n">
+      <c r="AL26" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AM26" s="4" t="n">
+      <c r="AM26" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AN26" s="4" t="n">
+      <c r="AN26" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AO26" s="4" t="n">
+      <c r="AO26" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AP26" s="4" t="n">
+      <c r="AP26" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AQ26" s="4" t="n">
+      <c r="AQ26" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AR26" s="4" t="n">
+      <c r="AR26" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AS26" s="5" t="n"/>
-      <c r="AT26" s="5" t="n"/>
-      <c r="AU26" s="5" t="n"/>
-      <c r="AV26" s="5" t="n"/>
-      <c r="AW26" s="4" t="n">
+      <c r="AS26" s="6" t="n"/>
+      <c r="AT26" s="6" t="n"/>
+      <c r="AU26" s="6" t="n"/>
+      <c r="AV26" s="6" t="n"/>
+      <c r="AW26" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AX26" s="4" t="n">
+      <c r="AX26" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AY26" s="4" t="n">
+      <c r="AY26" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AZ26" s="4" t="n">
+      <c r="AZ26" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BA26" s="4" t="n">
+      <c r="BA26" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BB26" s="4" t="n">
+      <c r="BB26" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BC26" s="4" t="n">
+      <c r="BC26" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="BD26" s="4" t="n">
+      <c r="BD26" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="BE26" s="5" t="n"/>
-      <c r="BF26" s="5" t="n"/>
-      <c r="BG26" s="5" t="n"/>
-      <c r="BH26" s="3" t="inlineStr">
+      <c r="BE26" s="6" t="n"/>
+      <c r="BF26" s="6" t="n"/>
+      <c r="BG26" s="6" t="n"/>
+      <c r="BH26" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="4" t="n">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K27" s="4" t="n">
+      <c r="K27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="P27" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="Q27" s="4" t="n">
+      <c r="Q27" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="R27" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="S27" s="4" t="n">
+      <c r="S27" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="T27" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="U27" s="4" t="n">
+      <c r="U27" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="V27" s="4" t="n">
+      <c r="V27" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="W27" s="4" t="n">
+      <c r="W27" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="X27" s="4" t="n">
+      <c r="X27" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Y27" s="4" t="n">
+      <c r="Y27" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="Z27" s="4" t="n">
+      <c r="Z27" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AA27" s="4" t="n">
+      <c r="AA27" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AB27" s="4" t="n">
+      <c r="AB27" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AC27" s="5" t="n"/>
-      <c r="AD27" s="5" t="n"/>
-      <c r="AE27" s="3" t="inlineStr">
+      <c r="AC27" s="6" t="n"/>
+      <c r="AD27" s="6" t="n"/>
+      <c r="AE27" s="4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="n">
+      <c r="AF27" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AG27" s="4" t="n">
+      <c r="AG27" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AH27" s="4" t="n">
+      <c r="AH27" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AI27" s="4" t="n">
+      <c r="AI27" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AJ27" s="4" t="n">
+      <c r="AJ27" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AK27" s="4" t="n">
+      <c r="AK27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AL27" s="4" t="n">
+      <c r="AL27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AM27" s="4" t="n">
+      <c r="AM27" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AN27" s="4" t="n">
+      <c r="AN27" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AO27" s="4" t="n">
+      <c r="AO27" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AP27" s="4" t="n">
+      <c r="AP27" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AQ27" s="4" t="n">
+      <c r="AQ27" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AR27" s="4" t="n">
+      <c r="AR27" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AS27" s="4" t="n">
+      <c r="AS27" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AT27" s="5" t="n"/>
-      <c r="AU27" s="5" t="n"/>
-      <c r="AV27" s="5" t="n"/>
-      <c r="AW27" s="4" t="n">
+      <c r="AT27" s="6" t="n"/>
+      <c r="AU27" s="6" t="n"/>
+      <c r="AV27" s="6" t="n"/>
+      <c r="AW27" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AX27" s="4" t="n">
+      <c r="AX27" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AY27" s="4" t="n">
+      <c r="AY27" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="AZ27" s="4" t="n">
+      <c r="AZ27" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BA27" s="4" t="n">
+      <c r="BA27" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="BB27" s="4" t="n">
+      <c r="BB27" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="BC27" s="4" t="n">
+      <c r="BC27" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="BD27" s="5" t="n"/>
-      <c r="BE27" s="5" t="n"/>
-      <c r="BF27" s="5" t="n"/>
-      <c r="BG27" s="5" t="n"/>
-      <c r="BH27" s="3" t="inlineStr">
+      <c r="BD27" s="6" t="n"/>
+      <c r="BE27" s="6" t="n"/>
+      <c r="BF27" s="6" t="n"/>
+      <c r="BG27" s="6" t="n"/>
+      <c r="BH27" s="4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="4" t="n">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="4" t="n">
+      <c r="K28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="3" t="inlineStr">
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="P28" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" s="4" t="n">
+      <c r="Q28" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="R28" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="S28" s="4" t="n">
+      <c r="S28" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="T28" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="U28" s="4" t="n">
+      <c r="U28" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="V28" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="W28" s="4" t="n">
+      <c r="W28" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="X28" s="4" t="n">
+      <c r="X28" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="Y28" s="4" t="n">
+      <c r="Y28" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="Z28" s="4" t="n">
+      <c r="Z28" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AA28" s="4" t="n">
+      <c r="AA28" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB28" s="4" t="n">
+      <c r="AB28" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AC28" s="5" t="n"/>
-      <c r="AD28" s="5" t="n"/>
-      <c r="AE28" s="3" t="inlineStr">
+      <c r="AC28" s="6" t="n"/>
+      <c r="AD28" s="6" t="n"/>
+      <c r="AE28" s="4" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="n">
+      <c r="AF28" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AG28" s="4" t="n">
+      <c r="AG28" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AH28" s="4" t="n">
+      <c r="AH28" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AI28" s="4" t="n">
+      <c r="AI28" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AJ28" s="4" t="n">
+      <c r="AJ28" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AK28" s="4" t="n">
+      <c r="AK28" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AL28" s="4" t="n">
+      <c r="AL28" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AM28" s="4" t="n">
+      <c r="AM28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AN28" s="4" t="n">
+      <c r="AN28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AO28" s="4" t="n">
+      <c r="AO28" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AP28" s="4" t="n">
+      <c r="AP28" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AQ28" s="4" t="n">
+      <c r="AQ28" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AR28" s="4" t="n">
+      <c r="AR28" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AS28" s="4" t="n">
+      <c r="AS28" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AT28" s="5" t="n"/>
-      <c r="AU28" s="5" t="n"/>
-      <c r="AV28" s="5" t="n"/>
-      <c r="AW28" s="4" t="n">
+      <c r="AT28" s="6" t="n"/>
+      <c r="AU28" s="6" t="n"/>
+      <c r="AV28" s="6" t="n"/>
+      <c r="AW28" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AX28" s="4" t="n">
+      <c r="AX28" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AY28" s="4" t="n">
+      <c r="AY28" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="AZ28" s="4" t="n">
+      <c r="AZ28" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="BA28" s="4" t="n">
+      <c r="BA28" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="BB28" s="5" t="n"/>
-      <c r="BC28" s="5" t="n"/>
-      <c r="BD28" s="5" t="n"/>
-      <c r="BE28" s="5" t="n"/>
-      <c r="BF28" s="5" t="n"/>
-      <c r="BG28" s="5" t="n"/>
-      <c r="BH28" s="3" t="inlineStr">
+      <c r="BB28" s="6" t="n"/>
+      <c r="BC28" s="6" t="n"/>
+      <c r="BD28" s="6" t="n"/>
+      <c r="BE28" s="6" t="n"/>
+      <c r="BF28" s="6" t="n"/>
+      <c r="BG28" s="6" t="n"/>
+      <c r="BH28" s="4" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="4" t="n">
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="4" t="n">
+      <c r="K29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="P29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="Q29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="R29" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="S29" s="4" t="n">
+      <c r="S29" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="T29" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="U29" s="4" t="n">
+      <c r="U29" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="V29" s="4" t="n">
+      <c r="V29" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="W29" s="4" t="n">
+      <c r="W29" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="X29" s="4" t="n">
+      <c r="X29" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="Y29" s="4" t="n">
+      <c r="Y29" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="Z29" s="4" t="n">
+      <c r="Z29" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AA29" s="4" t="n">
+      <c r="AA29" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AB29" s="4" t="n">
+      <c r="AB29" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AC29" s="4" t="n">
+      <c r="AC29" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AD29" s="5" t="n"/>
-      <c r="AE29" s="3" t="inlineStr">
+      <c r="AD29" s="6" t="n"/>
+      <c r="AE29" s="4" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="n">
+      <c r="AF29" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AG29" s="4" t="n">
+      <c r="AG29" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AH29" s="4" t="n">
+      <c r="AH29" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AI29" s="4" t="n">
+      <c r="AI29" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AJ29" s="4" t="n">
+      <c r="AJ29" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AK29" s="4" t="n">
+      <c r="AK29" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AL29" s="4" t="n">
+      <c r="AL29" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AM29" s="4" t="n">
+      <c r="AM29" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AN29" s="4" t="n">
+      <c r="AN29" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AO29" s="4" t="n">
+      <c r="AO29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AP29" s="4" t="n">
+      <c r="AP29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AQ29" s="4" t="n">
+      <c r="AQ29" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AR29" s="4" t="n">
+      <c r="AR29" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AS29" s="4" t="n">
+      <c r="AS29" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AT29" s="5" t="n"/>
-      <c r="AU29" s="5" t="n"/>
-      <c r="AV29" s="5" t="n"/>
-      <c r="AW29" s="4" t="n">
+      <c r="AT29" s="6" t="n"/>
+      <c r="AU29" s="6" t="n"/>
+      <c r="AV29" s="6" t="n"/>
+      <c r="AW29" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AX29" s="4" t="n">
+      <c r="AX29" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AY29" s="4" t="n">
+      <c r="AY29" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AZ29" s="5" t="n"/>
-      <c r="BA29" s="5" t="n"/>
-      <c r="BB29" s="5" t="n"/>
-      <c r="BC29" s="5" t="n"/>
-      <c r="BD29" s="5" t="n"/>
-      <c r="BE29" s="5" t="n"/>
-      <c r="BF29" s="5" t="n"/>
-      <c r="BG29" s="5" t="n"/>
-      <c r="BH29" s="3" t="inlineStr">
+      <c r="AZ29" s="6" t="n"/>
+      <c r="BA29" s="6" t="n"/>
+      <c r="BB29" s="6" t="n"/>
+      <c r="BC29" s="6" t="n"/>
+      <c r="BD29" s="6" t="n"/>
+      <c r="BE29" s="6" t="n"/>
+      <c r="BF29" s="6" t="n"/>
+      <c r="BG29" s="6" t="n"/>
+      <c r="BH29" s="4" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="4" t="n">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="3" t="inlineStr">
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="P30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="Q30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="R30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="S30" s="4" t="n">
+      <c r="S30" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="T30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="U30" s="4" t="n">
+      <c r="U30" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="V30" s="4" t="n">
+      <c r="V30" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="W30" s="4" t="n">
+      <c r="W30" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="X30" s="4" t="n">
+      <c r="X30" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="Y30" s="4" t="n">
+      <c r="Y30" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="Z30" s="4" t="n">
+      <c r="Z30" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AA30" s="4" t="n">
+      <c r="AA30" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AB30" s="4" t="n">
+      <c r="AB30" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AC30" s="4" t="n">
+      <c r="AC30" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AD30" s="5" t="n"/>
-      <c r="AE30" s="3" t="inlineStr">
+      <c r="AD30" s="6" t="n"/>
+      <c r="AE30" s="4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="n">
+      <c r="AF30" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AG30" s="4" t="n">
+      <c r="AG30" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AH30" s="4" t="n">
+      <c r="AH30" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AI30" s="4" t="n">
+      <c r="AI30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ30" s="4" t="n">
+      <c r="AJ30" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AK30" s="4" t="n">
+      <c r="AK30" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL30" s="4" t="n">
+      <c r="AL30" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AM30" s="4" t="n">
+      <c r="AM30" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AN30" s="4" t="n">
+      <c r="AN30" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AO30" s="4" t="n">
+      <c r="AO30" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AP30" s="4" t="n">
+      <c r="AP30" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AQ30" s="4" t="n">
+      <c r="AQ30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AR30" s="4" t="n">
+      <c r="AR30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AS30" s="4" t="n">
+      <c r="AS30" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AT30" s="4" t="n">
+      <c r="AT30" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AU30" s="5" t="n"/>
-      <c r="AV30" s="5" t="n"/>
-      <c r="AW30" s="4" t="n">
+      <c r="AU30" s="6" t="n"/>
+      <c r="AV30" s="6" t="n"/>
+      <c r="AW30" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AX30" s="4" t="n">
+      <c r="AX30" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AY30" s="4" t="n">
+      <c r="AY30" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="AZ30" s="5" t="n"/>
-      <c r="BA30" s="5" t="n"/>
-      <c r="BB30" s="5" t="n"/>
-      <c r="BC30" s="5" t="n"/>
-      <c r="BD30" s="5" t="n"/>
-      <c r="BE30" s="5" t="n"/>
-      <c r="BF30" s="5" t="n"/>
-      <c r="BG30" s="5" t="n"/>
-      <c r="BH30" s="3" t="inlineStr">
+      <c r="AZ30" s="6" t="n"/>
+      <c r="BA30" s="6" t="n"/>
+      <c r="BB30" s="6" t="n"/>
+      <c r="BC30" s="6" t="n"/>
+      <c r="BD30" s="6" t="n"/>
+      <c r="BE30" s="6" t="n"/>
+      <c r="BF30" s="6" t="n"/>
+      <c r="BG30" s="6" t="n"/>
+      <c r="BH30" s="4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="4" t="n">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="P31" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" s="4" t="n">
+      <c r="Q31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="R31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="S31" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="T31" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="U31" s="4" t="n">
+      <c r="U31" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="V31" s="4" t="n">
+      <c r="V31" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="W31" s="4" t="n">
+      <c r="W31" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="X31" s="4" t="n">
+      <c r="X31" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="Y31" s="4" t="n">
+      <c r="Y31" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="Z31" s="4" t="n">
+      <c r="Z31" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AA31" s="4" t="n">
+      <c r="AA31" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AB31" s="4" t="n">
+      <c r="AB31" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AC31" s="4" t="n">
+      <c r="AC31" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AD31" s="5" t="n"/>
-      <c r="AE31" s="3" t="inlineStr">
+      <c r="AD31" s="6" t="n"/>
+      <c r="AE31" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="n">
+      <c r="AF31" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AG31" s="4" t="n">
+      <c r="AG31" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AH31" s="4" t="n">
+      <c r="AH31" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AI31" s="4" t="n">
+      <c r="AI31" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AJ31" s="4" t="n">
+      <c r="AJ31" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AK31" s="4" t="n">
+      <c r="AK31" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AL31" s="4" t="n">
+      <c r="AL31" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AM31" s="4" t="n">
+      <c r="AM31" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AN31" s="4" t="n">
+      <c r="AN31" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AO31" s="4" t="n">
+      <c r="AO31" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AP31" s="4" t="n">
+      <c r="AP31" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AQ31" s="4" t="n">
+      <c r="AQ31" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AR31" s="4" t="n">
+      <c r="AR31" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="AS31" s="4" t="n">
+      <c r="AS31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="AT31" s="5" t="n"/>
-      <c r="AU31" s="5" t="n"/>
-      <c r="AV31" s="5" t="n"/>
-      <c r="AW31" s="4" t="n">
+      <c r="AT31" s="6" t="n"/>
+      <c r="AU31" s="6" t="n"/>
+      <c r="AV31" s="6" t="n"/>
+      <c r="AW31" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="AX31" s="4" t="n">
+      <c r="AX31" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="AY31" s="4" t="n">
+      <c r="AY31" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="AZ31" s="5" t="n"/>
-      <c r="BA31" s="5" t="n"/>
-      <c r="BB31" s="5" t="n"/>
-      <c r="BC31" s="5" t="n"/>
-      <c r="BD31" s="5" t="n"/>
-      <c r="BE31" s="5" t="n"/>
-      <c r="BF31" s="5" t="n"/>
-      <c r="BG31" s="5" t="n"/>
-      <c r="BH31" s="3" t="inlineStr">
+      <c r="AZ31" s="6" t="n"/>
+      <c r="BA31" s="6" t="n"/>
+      <c r="BB31" s="6" t="n"/>
+      <c r="BC31" s="6" t="n"/>
+      <c r="BD31" s="6" t="n"/>
+      <c r="BE31" s="6" t="n"/>
+      <c r="BF31" s="6" t="n"/>
+      <c r="BG31" s="6" t="n"/>
+      <c r="BH31" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="3" t="inlineStr">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="P32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="Q32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="R32" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="S32" s="4" t="n">
+      <c r="S32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="T32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="U32" s="4" t="n">
+      <c r="U32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="V32" s="4" t="n">
+      <c r="V32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="W32" s="4" t="n">
+      <c r="W32" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="X32" s="4" t="n">
+      <c r="X32" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="Y32" s="4" t="n">
+      <c r="Y32" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Z32" s="4" t="n">
+      <c r="Z32" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="AA32" s="4" t="n">
+      <c r="AA32" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="AB32" s="4" t="n">
+      <c r="AB32" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AC32" s="4" t="n">
+      <c r="AC32" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AD32" s="5" t="n"/>
-      <c r="AE32" s="3" t="inlineStr">
+      <c r="AD32" s="6" t="n"/>
+      <c r="AE32" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="n">
+      <c r="AF32" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AG32" s="4" t="n">
+      <c r="AG32" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AH32" s="4" t="n">
+      <c r="AH32" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AI32" s="4" t="n">
+      <c r="AI32" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AJ32" s="4" t="n">
+      <c r="AJ32" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AK32" s="4" t="n">
+      <c r="AK32" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AL32" s="4" t="n">
+      <c r="AL32" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AM32" s="4" t="n">
+      <c r="AM32" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AN32" s="4" t="n">
+      <c r="AN32" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AO32" s="4" t="n">
+      <c r="AO32" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AP32" s="4" t="n">
+      <c r="AP32" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AQ32" s="4" t="n">
+      <c r="AQ32" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AR32" s="4" t="n">
+      <c r="AR32" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="AS32" s="4" t="n">
+      <c r="AS32" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="AT32" s="5" t="n"/>
-      <c r="AU32" s="5" t="n"/>
-      <c r="AV32" s="5" t="n"/>
-      <c r="AW32" s="5" t="n"/>
-      <c r="AX32" s="5" t="n"/>
-      <c r="AY32" s="5" t="n"/>
-      <c r="AZ32" s="5" t="n"/>
-      <c r="BA32" s="5" t="n"/>
-      <c r="BB32" s="5" t="n"/>
-      <c r="BC32" s="5" t="n"/>
-      <c r="BD32" s="5" t="n"/>
-      <c r="BE32" s="5" t="n"/>
-      <c r="BF32" s="5" t="n"/>
-      <c r="BG32" s="5" t="n"/>
-      <c r="BH32" s="3" t="inlineStr">
+      <c r="AT32" s="6" t="n"/>
+      <c r="AU32" s="6" t="n"/>
+      <c r="AV32" s="6" t="n"/>
+      <c r="AW32" s="6" t="n"/>
+      <c r="AX32" s="6" t="n"/>
+      <c r="AY32" s="6" t="n"/>
+      <c r="AZ32" s="6" t="n"/>
+      <c r="BA32" s="6" t="n"/>
+      <c r="BB32" s="6" t="n"/>
+      <c r="BC32" s="6" t="n"/>
+      <c r="BD32" s="6" t="n"/>
+      <c r="BE32" s="6" t="n"/>
+      <c r="BF32" s="6" t="n"/>
+      <c r="BG32" s="6" t="n"/>
+      <c r="BH32" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="4" t="n">
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="6" t="n"/>
+      <c r="R33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S33" s="4" t="n">
+      <c r="S33" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="T33" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="U33" s="4" t="n">
+      <c r="U33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="V33" s="4" t="n">
+      <c r="V33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W33" s="4" t="n">
+      <c r="W33" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="X33" s="4" t="n">
+      <c r="X33" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="Y33" s="4" t="n">
+      <c r="Y33" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="Z33" s="4" t="n">
+      <c r="Z33" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="AA33" s="4" t="n">
+      <c r="AA33" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="AB33" s="4" t="n">
+      <c r="AB33" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="AC33" s="4" t="n">
+      <c r="AC33" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="AD33" s="4" t="n">
+      <c r="AD33" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="AE33" s="4" t="n">
+      <c r="AE33" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AF33" s="4" t="n">
+      <c r="AF33" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AG33" s="4" t="n">
+      <c r="AG33" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="AH33" s="4" t="n">
+      <c r="AH33" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AI33" s="4" t="n">
+      <c r="AI33" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="AJ33" s="4" t="n">
+      <c r="AJ33" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="AK33" s="4" t="n">
+      <c r="AK33" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AL33" s="4" t="n">
+      <c r="AL33" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="AM33" s="4" t="n">
+      <c r="AM33" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="AN33" s="4" t="n">
+      <c r="AN33" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="AO33" s="4" t="n">
+      <c r="AO33" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AP33" s="4" t="n">
+      <c r="AP33" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="AQ33" s="4" t="n">
+      <c r="AQ33" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="AR33" s="5" t="n"/>
-      <c r="AS33" s="5" t="n"/>
-      <c r="AT33" s="5" t="n"/>
-      <c r="AU33" s="5" t="n"/>
-      <c r="AV33" s="5" t="n"/>
-      <c r="AW33" s="5" t="n"/>
-      <c r="AX33" s="5" t="n"/>
-      <c r="AY33" s="5" t="n"/>
-      <c r="AZ33" s="5" t="n"/>
-      <c r="BA33" s="5" t="n"/>
-      <c r="BB33" s="5" t="n"/>
-      <c r="BC33" s="5" t="n"/>
-      <c r="BD33" s="5" t="n"/>
-      <c r="BE33" s="5" t="n"/>
-      <c r="BF33" s="5" t="n"/>
-      <c r="BG33" s="5" t="n"/>
-      <c r="BH33" s="3" t="inlineStr">
+      <c r="AR33" s="6" t="n"/>
+      <c r="AS33" s="6" t="n"/>
+      <c r="AT33" s="6" t="n"/>
+      <c r="AU33" s="6" t="n"/>
+      <c r="AV33" s="6" t="n"/>
+      <c r="AW33" s="6" t="n"/>
+      <c r="AX33" s="6" t="n"/>
+      <c r="AY33" s="6" t="n"/>
+      <c r="AZ33" s="6" t="n"/>
+      <c r="BA33" s="6" t="n"/>
+      <c r="BB33" s="6" t="n"/>
+      <c r="BC33" s="6" t="n"/>
+      <c r="BD33" s="6" t="n"/>
+      <c r="BE33" s="6" t="n"/>
+      <c r="BF33" s="6" t="n"/>
+      <c r="BG33" s="6" t="n"/>
+      <c r="BH33" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
@@ -4845,7 +4837,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:BH1"/>
-    <mergeCell ref="F2:BH2"/>
+    <mergeCell ref="F2:BE2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Sayajirao_Hall_Seat_Template.xlsx
+++ b/Sayajirao_Hall_Seat_Template.xlsx
@@ -43,7 +43,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00888888"/>
+      <color rgb="00999999"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -551,7 +551,7 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>S T A G E</t>
         </is>
@@ -4837,7 +4837,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:BH1"/>
-    <mergeCell ref="F2:BE2"/>
+    <mergeCell ref="G2:BH2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
